--- a/XD8/Đoạn 4/4. K98 Base - XD8 đoạn 4.xlsx
+++ b/XD8/Đoạn 4/4. K98 Base - XD8 đoạn 4.xlsx
@@ -17,6 +17,9 @@
     <sheet name="Base B" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="KL Basa B" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rIdExt1"/>
+  </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Base A'!$A$1:$S$69</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Base A'!$21:$22</definedName>
@@ -1364,6 +1367,418 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IN"/>
+      <sheetName val="Tuyến XD8"/>
+      <sheetName val="1. PL đường đen"/>
+      <sheetName val="2. Cao độ đào nền"/>
+      <sheetName val="2. KL đào nền"/>
+      <sheetName val="3. KTHH vải lọc"/>
+      <sheetName val="3. KL vải lọc"/>
+      <sheetName val="chạy VL"/>
+      <sheetName val="KL tưới nhựa"/>
+      <sheetName val="CĐ mặt đường"/>
+      <sheetName val="KL BTN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="A3">
+            <v>84</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+609,11 -:- Km0+724,11</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v xml:space="preserve">ngày 26 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v xml:space="preserve">84.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>85</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v xml:space="preserve">ngày 27 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v xml:space="preserve">85.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>86</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v xml:space="preserve">ngày 28 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v xml:space="preserve">86.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>87</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v xml:space="preserve">ngày 28 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v xml:space="preserve">87.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>88</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v xml:space="preserve">ngày 29 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v xml:space="preserve">88.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>89</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v xml:space="preserve">ngày 29 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v xml:space="preserve">89.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>90</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v xml:space="preserve">ngày 30 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v xml:space="preserve">90.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>91</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v xml:space="preserve">ngày 30 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v xml:space="preserve">91.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>92</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v xml:space="preserve">ngày 01 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v xml:space="preserve">92.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>93</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v xml:space="preserve">ngày 01 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v xml:space="preserve">93.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>94</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v xml:space="preserve">ngày 02 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v xml:space="preserve">94.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>95</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v xml:space="preserve">ngày 02 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v xml:space="preserve">95.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>96</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v xml:space="preserve">ngày 03 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v xml:space="preserve">96.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>97</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v xml:space="preserve">ngày 03 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v xml:space="preserve">97.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>98</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+609,11 - Km0+724,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v xml:space="preserve">ngày 04 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v xml:space="preserve">98.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>99</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v xml:space="preserve">ngày 05 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v xml:space="preserve">99.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>100</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v xml:space="preserve">ngày 05 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v xml:space="preserve">100.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>101</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v xml:space="preserve">ngày 06 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v xml:space="preserve">101.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>102</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v xml:space="preserve">ngày 06 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v xml:space="preserve">102.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>103</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v xml:space="preserve">ngày 07 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v xml:space="preserve">103.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>104</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v xml:space="preserve">ngày 07 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v xml:space="preserve">104.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>105</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v xml:space="preserve">ngày 08 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v xml:space="preserve">105.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>106</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+609,11 - Km0+724,11</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v xml:space="preserve">ngày 08 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G25" t="str">
+            <v xml:space="preserve">106.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>107</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
+          </cell>
+          <cell r="D26" t="str">
+            <v xml:space="preserve">ngày 10 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G26" t="str">
+            <v xml:space="preserve">107.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>108</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v xml:space="preserve">ngày 12 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G27" t="str">
+            <v xml:space="preserve">108.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>109</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v xml:space="preserve">ngày 15 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G28" t="str">
+            <v xml:space="preserve">109.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>110</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v xml:space="preserve">ngày 17 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G29" t="str">
+            <v xml:space="preserve">110.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1587,8 +2002,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 99.NĐXD8/CVXD ngày 05 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1611,6 +2027,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>99</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -1723,8 +2142,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>7</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -3393,8 +3813,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>1</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 99.NĐXD8/CVXD ngày 05 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -3423,6 +3844,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>99</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -4377,8 +4801,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>7</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -9034,8 +9459,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>43</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 101.NĐXD8/CVXD ngày 06 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9058,6 +9484,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>101</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -9170,8 +9599,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -10879,8 +11309,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>43</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 101.NĐXD8/CVXD ngày 06 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -10909,6 +11340,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>101</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -11863,8 +12297,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>44</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16444,8 +16879,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>45</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 103.NĐXD8/CVXD ngày 07 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -16468,6 +16904,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -16580,8 +17019,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>46</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -18289,8 +18729,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>45</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 103.NĐXD8/CVXD ngày 07 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -18319,6 +18760,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -19273,8 +19717,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>46</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -23854,8 +24299,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>47</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 106.NĐXD8/CVXD ngày 08 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -23878,6 +24324,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>106</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -23990,8 +24439,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>48</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -25699,8 +26149,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>47</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 106.NĐXD8/CVXD ngày 08 tháng 10 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -25729,6 +26180,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>106</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -26683,8 +27137,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>48</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+609,11 - Km0+724,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>

--- a/XD8/Đoạn 4/4. K98 Base - XD8 đoạn 4.xlsx
+++ b/XD8/Đoạn 4/4. K98 Base - XD8 đoạn 4.xlsx
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Nguyễn Xuân Hưng</t>
   </si>
   <si>
-    <t xml:space="preserve">Trần Mạnh Tùng</t>
+    <t xml:space="preserve">Lê Quốc Huy</t>
   </si>
   <si>
     <t xml:space="preserve">PHỤ LỤC KHỐI LƯỢNG </t>
